--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,507 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123538140</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57500</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572581</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6568467</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123538069</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90986</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572581</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6568467</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123537973</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91521</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572581</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6568467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer i södersluttning längs bergvägg.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123537924</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57851</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572581</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568467</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123525479</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>123538140</v>
       </c>
       <c r="B3" t="n">
-        <v>57500</v>
+        <v>57506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123538069</v>
+        <v>123537973</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>91538</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123537973</v>
+        <v>123538069</v>
       </c>
       <c r="B5" t="n">
-        <v>91521</v>
+        <v>91003</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,25 +1060,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3884</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
         <v>123537924</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123663730</v>
+        <v>123664432</v>
       </c>
       <c r="B7" t="n">
-        <v>57397</v>
+        <v>5490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,15 +1334,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1352,17 +1349,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572547</v>
+        <v>572573</v>
       </c>
       <c r="R7" t="n">
-        <v>6568512</v>
+        <v>6568471</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,12 +1398,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
+          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123664432</v>
+        <v>123663730</v>
       </c>
       <c r="B8" t="n">
-        <v>5489</v>
+        <v>57403</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,21 +1446,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1471,12 +1468,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572573</v>
+        <v>572547</v>
       </c>
       <c r="R8" t="n">
-        <v>6568471</v>
+        <v>6568512</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
+          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>123525479</v>
       </c>
       <c r="B2" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123538140</v>
+        <v>123537973</v>
       </c>
       <c r="B3" t="n">
-        <v>57506</v>
+        <v>91543</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123537973</v>
+        <v>123537924</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>57860</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,30 +935,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123538069</v>
+        <v>123538140</v>
       </c>
       <c r="B5" t="n">
-        <v>91003</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,34 +1055,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123537924</v>
+        <v>123538069</v>
       </c>
       <c r="B6" t="n">
-        <v>57857</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1259,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,7 +1299,7 @@
         <v>123664432</v>
       </c>
       <c r="B7" t="n">
-        <v>5490</v>
+        <v>5492</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>123663730</v>
       </c>
       <c r="B8" t="n">
-        <v>57403</v>
+        <v>57406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1564,6 +1564,374 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123867853</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarnstallet, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572554</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568530</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123868684</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572565</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568441</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123868771</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100680</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjälmaregården, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572577</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6568430</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123525479</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123537973</v>
+        <v>123538069</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +922,7 @@
         <v>123537924</v>
       </c>
       <c r="B4" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         <v>123538140</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123538069</v>
+        <v>123537973</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,25 +1184,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123664432</v>
+        <v>123663730</v>
       </c>
       <c r="B7" t="n">
-        <v>5492</v>
+        <v>57407</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101410</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,12 +1334,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1349,17 +1352,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572573</v>
+        <v>572547</v>
       </c>
       <c r="R7" t="n">
-        <v>6568471</v>
+        <v>6568512</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,7 +1391,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1398,12 +1401,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
+          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123663730</v>
+        <v>123664432</v>
       </c>
       <c r="B8" t="n">
-        <v>57406</v>
+        <v>5492</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1446,21 +1449,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100067</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1468,15 +1471,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572547</v>
+        <v>572573</v>
       </c>
       <c r="R8" t="n">
-        <v>6568512</v>
+        <v>6568471</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
+          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,10 +1567,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867853</v>
+        <v>123868684</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>100682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,53 +1579,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572554</v>
+        <v>572565</v>
       </c>
       <c r="R9" t="n">
-        <v>6568530</v>
+        <v>6568441</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1691,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B10" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,20 +1728,24 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R10" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123868771</v>
+        <v>123867853</v>
       </c>
       <c r="B11" t="n">
-        <v>100680</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,53 +1823,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572577</v>
+        <v>572554</v>
       </c>
       <c r="R11" t="n">
-        <v>6568430</v>
+        <v>6568530</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123538069</v>
+        <v>123537973</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>91545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123537924</v>
+        <v>123538069</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +931,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123538140</v>
+        <v>123537924</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,21 +1059,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123537973</v>
+        <v>123538140</v>
       </c>
       <c r="B6" t="n">
-        <v>91545</v>
+        <v>57510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,30 +1183,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3884</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123663730</v>
+        <v>123664432</v>
       </c>
       <c r="B7" t="n">
-        <v>57407</v>
+        <v>5492</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>101410</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1334,15 +1334,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2K</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1352,17 +1349,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572547</v>
+        <v>572573</v>
       </c>
       <c r="R7" t="n">
-        <v>6568512</v>
+        <v>6568471</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1388,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1401,12 +1398,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
+          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1433,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123664432</v>
+        <v>123663730</v>
       </c>
       <c r="B8" t="n">
-        <v>5492</v>
+        <v>57407</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,21 +1446,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101410</v>
+        <v>100067</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1471,12 +1468,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572573</v>
+        <v>572547</v>
       </c>
       <c r="R8" t="n">
-        <v>6568471</v>
+        <v>6568512</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ovala kläckhål 3-4mm på grov gammal tall i söderläge. Skogen är avverkningsanmäld</t>
+          <t>Havsörn har noterats i skogsområdet vid flera tillfällen. Örnen lyfte från en äldre tall i sluttningen. Skogen är avverkningsanmäld.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,10 +1567,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868684</v>
+        <v>123867853</v>
       </c>
       <c r="B9" t="n">
-        <v>100682</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,49 +1579,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572565</v>
+        <v>572554</v>
       </c>
       <c r="R9" t="n">
-        <v>6568441</v>
+        <v>6568530</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,7 +1694,7 @@
         <v>123868771</v>
       </c>
       <c r="B10" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1811,10 +1815,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123867853</v>
+        <v>123868684</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,53 +1827,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572554</v>
+        <v>572565</v>
       </c>
       <c r="R11" t="n">
-        <v>6568530</v>
+        <v>6568441</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123537973</v>
+        <v>123538140</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123538069</v>
+        <v>123537973</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>91545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,25 +936,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1001,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123537924</v>
+        <v>123538069</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>91010</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,39 +1060,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123538140</v>
+        <v>123537924</v>
       </c>
       <c r="B6" t="n">
-        <v>57510</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,21 +1188,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1209,7 +1214,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1254,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,12 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1567,10 +1567,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123867853</v>
+        <v>123868684</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,53 +1579,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572554</v>
+        <v>572565</v>
       </c>
       <c r="R9" t="n">
-        <v>6568530</v>
+        <v>6568441</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1815,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123868684</v>
+        <v>123867853</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1827,49 +1823,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572565</v>
+        <v>572554</v>
       </c>
       <c r="R11" t="n">
-        <v>6568441</v>
+        <v>6568530</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123538140</v>
+        <v>123537924</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,21 +811,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,7 +837,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1048,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123538069</v>
+        <v>123538140</v>
       </c>
       <c r="B5" t="n">
-        <v>91010</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,34 +1055,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123537924</v>
+        <v>123538069</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,39 +1184,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1259,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1567,7 +1567,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B9" t="n">
         <v>100257</v>
@@ -1608,20 +1608,24 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,7 +1691,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B10" t="n">
         <v>100257</v>
@@ -1728,24 +1732,20 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R10" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123537924</v>
+        <v>123537973</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>91545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,35 +811,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>3884</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -882,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123537973</v>
+        <v>123538140</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1001,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123538140</v>
+        <v>123537924</v>
       </c>
       <c r="B5" t="n">
-        <v>57510</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,7 +1090,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1130,7 +1135,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1145,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1567,10 +1567,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868771</v>
+        <v>123867853</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1579,53 +1579,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572554</v>
       </c>
       <c r="R9" t="n">
-        <v>6568430</v>
+        <v>6568530</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123867853</v>
+        <v>123868771</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,53 +1823,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572554</v>
+        <v>572577</v>
       </c>
       <c r="R11" t="n">
-        <v>6568530</v>
+        <v>6568430</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123537973</v>
+        <v>123538069</v>
       </c>
       <c r="B3" t="n">
-        <v>91545</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i södersluttning längs bergvägg.</t>
+          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123538140</v>
+        <v>123537924</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -961,7 +961,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123537924</v>
+        <v>123538140</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>57510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1059,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1135,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1145,7 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hålträd med spillning från gröngöling. Skogen planeras avverkas av Skogssällskapet.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123538069</v>
+        <v>123537973</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>91545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,25 +1184,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>3884</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tallticka växer på flera tallar i sluttningen. Skogen är avverknkngsanmäld av Skogssällskapet.</t>
+          <t>Växer i södersluttning längs bergvägg.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -1567,7 +1567,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1608,20 +1608,24 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1687,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123867853</v>
+        <v>123868684</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,53 +1703,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572554</v>
+        <v>572565</v>
       </c>
       <c r="R10" t="n">
-        <v>6568530</v>
+        <v>6568441</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123868771</v>
+        <v>123867853</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,53 +1823,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572577</v>
+        <v>572554</v>
       </c>
       <c r="R11" t="n">
-        <v>6568430</v>
+        <v>6568530</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -1691,10 +1691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123868684</v>
+        <v>123867853</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1703,49 +1703,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hjälmaregården, Srm</t>
+          <t>Kvarnstallet, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572565</v>
+        <v>572554</v>
       </c>
       <c r="R10" t="n">
-        <v>6568441</v>
+        <v>6568530</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1774,7 +1778,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,10 +1815,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123867853</v>
+        <v>123868684</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,53 +1827,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnstallet, Srm</t>
+          <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572554</v>
+        <v>572565</v>
       </c>
       <c r="R11" t="n">
-        <v>6568530</v>
+        <v>6568441</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -1567,7 +1567,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1608,24 +1608,20 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R9" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1650,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1660,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1815,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1856,20 +1852,24 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R11" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 2517-2025 artfynd.xlsx
+++ b/artfynd/A 2517-2025 artfynd.xlsx
@@ -1567,7 +1567,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123868684</v>
+        <v>123868771</v>
       </c>
       <c r="B9" t="n">
         <v>100279</v>
@@ -1608,20 +1608,24 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572565</v>
+        <v>572577</v>
       </c>
       <c r="R9" t="n">
-        <v>6568441</v>
+        <v>6568430</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1811,7 +1815,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123868771</v>
+        <v>123868684</v>
       </c>
       <c r="B11" t="n">
         <v>100279</v>
@@ -1852,24 +1856,20 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hjälmaregården, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572577</v>
+        <v>572565</v>
       </c>
       <c r="R11" t="n">
-        <v>6568430</v>
+        <v>6568441</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
